--- a/reports/pdf_rolling5_20260731.xlsx
+++ b/reports/pdf_rolling5_20260731.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,438억   ·   현금 449억(12.7%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 9종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 451억(12.7%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>380259360</v>
+        <v>381781920</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-11684703600</v>
+        <v>-11731489200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>47</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>997751250</v>
+        <v>1001746250</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-59</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2876320800</v>
+        <v>-2887837600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1982915100</v>
+        <v>1990854700</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-36</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-663176160</v>
+        <v>-665831520</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>944354700</v>
+        <v>948135900</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-458391150</v>
+        <v>-460226550</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>921327750</v>
+        <v>925016750</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-763385850</v>
+        <v>-766442450</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>642856500</v>
+        <v>645430500</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2414083500</v>
+        <v>-2423749500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>629220150</v>
+        <v>631739550</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-698500800</v>
+        <v>-701297600</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>892306800</v>
+        <v>895879600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-550548900</v>
+        <v>-552753300</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>791208000</v>
+        <v>794376000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2235762000</v>
+        <v>-2244714000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-491008500</v>
+        <v>-492974500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,104억   ·   현금 39억(1.3%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,004억   ·   현금 39억(1.3%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1111,7 +1111,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 98억(5.2%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 4종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 97억(5.2%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1207,7 +1207,7 @@
         <v>85</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1742308750</v>
+        <v>1734722500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>-110</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-5184036000</v>
+        <v>-5161464000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>31</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1507945400</v>
+        <v>1501379600</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>-50</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-3445000000</v>
+        <v>-3430000000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>4236661000</v>
+        <v>4218214000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>-49</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-290682210</v>
+        <v>-289416540</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>770991000</v>
+        <v>767634000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,829억   ·   현금 100억(5.4%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 101억(5.4%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1456,7 +1456,7 @@
         <v>328</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>6640819200</v>
+        <v>6680704000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>-246</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-15564420000</v>
+        <v>-15657900000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>116</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1765299600</v>
+        <v>1775902000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>-7</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-3559437000</v>
+        <v>-3580815000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>71</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2116048500</v>
+        <v>2128757500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>41</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>3816013500</v>
+        <v>3838932500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 218억   ·   현금 21억(9.1%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 11종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 21억(9.5%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 11종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1689,11 +1689,11 @@
         <v>62</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>12604600</v>
+        <v>12321880</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.45%→0.53%</t>
+          <t>0.46%→0.54%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.88%→0.00%</t>
+          <t>3.01%→0.00%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1733,11 +1733,11 @@
         <v>49</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>54891760</v>
+        <v>57870960</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.30%</t>
+          <t>3.25%→3.64%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1754,11 +1754,11 @@
         <v>-145</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-35098700</v>
+        <v>-35319100</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>2.88%→2.81%</t>
+          <t>3.03%→2.96%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1777,11 +1777,11 @@
         <v>28</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>50008000</v>
+        <v>47241600</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.28%→2.58%</t>
+          <t>2.25%→2.56%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1798,11 +1798,11 @@
         <v>-91</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-43778280</v>
+        <v>-44884840</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.85%</t>
+          <t>1.10%→0.92%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1821,11 +1821,11 @@
         <v>27</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>117169200</v>
+        <v>103831200</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>3.11%→3.76%</t>
+          <t>2.88%→3.49%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1842,11 +1842,11 @@
         <v>-77</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-77246400</v>
+        <v>-68292840</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -1865,11 +1865,11 @@
         <v>13</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>21291400</v>
+        <v>20846800</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.74%→0.86%</t>
+          <t>0.75%→0.88%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1886,11 +1886,11 @@
         <v>-30</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-57000000</v>
+        <v>-56202000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>3.18%→3.01%</t>
+          <t>3.28%→3.11%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1909,11 +1909,11 @@
         <v>11</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>46732400</v>
+        <v>43304800</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.66%→1.93%</t>
+          <t>1.61%→1.87%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1930,11 +1930,11 @@
         <v>-11</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-39501000</v>
+        <v>-36867600</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>2.46%→2.34%</t>
+          <t>2.40%→2.29%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>9</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>78591600</v>
+        <v>69357600</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.68%→3.14%</t>
+          <t>2.48%→2.90%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1974,11 +1974,11 @@
         <v>-8</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-29579200</v>
+        <v>-27785600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.52%</t>
+          <t>0.63%→0.52%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1997,11 +1997,11 @@
         <v>9</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>56156400</v>
+        <v>52804800</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.83%</t>
+          <t>2.45%→2.79%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2018,7 +2018,7 @@
         <v>-7</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-44102800</v>
+        <v>-41442800</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2041,11 +2041,11 @@
         <v>8</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>17966400</v>
+        <v>16963200</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>7.13%→7.43%</t>
+          <t>7.04%→7.36%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2062,11 +2062,11 @@
         <v>-6</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-128820000</v>
+        <v>-127452000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.42%</t>
+          <t>2.04%→1.47%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>7</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>60807600</v>
+        <v>53200000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.87%→3.25%</t>
+          <t>2.62%→2.98%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2106,11 +2106,11 @@
         <v>-6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-107388000</v>
+        <v>-103512000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.52%</t>
+          <t>1.99%→1.54%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>4</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>27968000</v>
+        <v>25596800</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.16%</t>
+          <t>0.95%→1.11%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2150,7 +2150,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 433억   ·   현금 36억(8.3%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 4종목  /  매도 6종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 37억(8.3%)      오늘 2026-07-31  vs  5일전 2026-07-24      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2246,7 +2246,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>475167000</v>
+        <v>483806400</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>-607</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-801240000</v>
+        <v>-815808000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>10</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>132880000</v>
+        <v>135296000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>-593</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-739708200</v>
+        <v>-753157440</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>9</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>222255000</v>
+        <v>226296000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>-518</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-418233200</v>
+        <v>-425837440</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1175790000</v>
+        <v>1197168000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>-104</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-240812000</v>
+        <v>-245190400</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>-33</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-689700000</v>
+        <v>-702240000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>-9</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-276705000</v>
+        <v>-281736000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260731.xlsx
+++ b/reports/pdf_rolling5_20260731.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈  (신규)</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1990854700</v>
+        <v>948135900</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.64%</t>
+          <t>3.40%→3.29%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→46</t>
+          <t>449→495</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>하나머티리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>948135900</v>
+        <v>1990854700</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.29%</t>
+          <t>0.00%→0.64%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>449→495</t>
+          <t>0→46</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260731.xlsx
+++ b/reports/pdf_rolling5_20260731.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>하나머티리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>948135900</v>
+        <v>1990854700</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.29%</t>
+          <t>0.00%→0.64%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>449→495</t>
+          <t>0→46</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈  (신규)</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1990854700</v>
+        <v>948135900</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.64%</t>
+          <t>3.40%→3.29%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>0→46</t>
+          <t>449→495</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260731.xlsx
+++ b/reports/pdf_rolling5_20260731.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈  (신규)</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1990854700</v>
+        <v>948135900</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.64%</t>
+          <t>3.40%→3.29%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→46</t>
+          <t>449→495</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>하나머티리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>948135900</v>
+        <v>1990854700</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.29%</t>
+          <t>0.00%→0.64%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>449→495</t>
+          <t>0→46</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1946,23 +1946,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>69357600</v>
+        <v>52804800</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.90%</t>
+          <t>2.45%→2.79%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>67→76</t>
+          <t>87→96</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -1990,23 +1990,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>52804800</v>
+        <v>69357600</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.45%→2.79%</t>
+          <t>2.48%→2.90%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>87→96</t>
+          <t>67→76</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260731.xlsx
+++ b/reports/pdf_rolling5_20260731.xlsx
@@ -1946,23 +1946,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>52804800</v>
+        <v>69357600</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.45%→2.79%</t>
+          <t>2.48%→2.90%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>87→96</t>
+          <t>67→76</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -1990,23 +1990,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>69357600</v>
+        <v>52804800</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.90%</t>
+          <t>2.45%→2.79%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>67→76</t>
+          <t>87→96</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
